--- a/flashswf/arts/怪物掉落表.xlsx
+++ b/flashswf/arts/怪物掉落表.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Game\闪7重置计划\resources\flashswf\arts\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Workspaces\Flash+An\resources\flashswf\arts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D203609-F247-4EED-8837-31C28DBD6406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D54C28C6-1613-4F2A-ABE1-E72E2674B0AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="things1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="98">
   <si>
     <t>敌人类型</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -219,10 +219,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>防沙皮革</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>牛仔的左轮</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -400,6 +396,50 @@
   </si>
   <si>
     <t>异形龙骨碎片*15</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>除大僵尸外已全部迁移至敌人属性表和对应关卡文件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>已全部迁移至敌人属性表</t>
+  </si>
+  <si>
+    <t>除boss和黑铁死士外已全部迁移至敌人属性表</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>材料部分已配置到</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>xml</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，装备后面再考虑</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>战术鱼骨零件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>KM型消声器</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -407,7 +447,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -462,6 +502,12 @@
       <name val="微软雅黑"/>
       <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="7">
@@ -721,9 +767,6 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -750,6 +793,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1032,22 +1078,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D40"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="17.125" customWidth="1"/>
-    <col min="2" max="2" width="18.625" customWidth="1"/>
-    <col min="4" max="4" width="15.625" customWidth="1"/>
+    <col min="1" max="1" width="17.109375" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="39" x14ac:dyDescent="0.75">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:4" ht="33">
+      <c r="A1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="29"/>
-    </row>
-    <row r="2" spans="1:4" s="1" customFormat="1" ht="25.5" x14ac:dyDescent="0.5">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="28"/>
+    </row>
+    <row r="2" spans="1:4" s="1" customFormat="1" ht="22.2">
       <c r="A2" s="18" t="s">
         <v>0</v>
       </c>
@@ -1061,7 +1107,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
       <c r="A3" s="13" t="s">
         <v>5</v>
       </c>
@@ -1075,8 +1121,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A4" s="30" t="s">
+    <row r="4" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
+      <c r="A4" s="29" t="s">
         <v>8</v>
       </c>
       <c r="B4" s="4" t="s">
@@ -1089,8 +1135,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A5" s="31"/>
+    <row r="5" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
+      <c r="A5" s="30"/>
       <c r="B5" s="7" t="s">
         <v>9</v>
       </c>
@@ -1101,8 +1147,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A6" s="32"/>
+    <row r="6" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
+      <c r="A6" s="31"/>
       <c r="B6" s="10" t="s">
         <v>10</v>
       </c>
@@ -1113,7 +1159,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
       <c r="A7" s="13" t="s">
         <v>11</v>
       </c>
@@ -1127,7 +1173,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
       <c r="A8" s="17" t="s">
         <v>12</v>
       </c>
@@ -1141,7 +1187,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
       <c r="A9" s="17" t="s">
         <v>14</v>
       </c>
@@ -1155,7 +1201,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
       <c r="A10" s="17" t="s">
         <v>15</v>
       </c>
@@ -1169,36 +1215,40 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="17" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="18" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="19" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="20" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="21" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="22" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="23" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="24" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="25" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="26" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="27" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="28" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="29" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="30" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="31" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="32" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="33" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="34" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="35" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="36" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="37" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="38" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="39" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="40" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
+    <row r="11" spans="1:4" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="12" spans="1:4" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="13" spans="1:4" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="14" spans="1:4" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="15" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
+      <c r="A15" s="35" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="17" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="18" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="19" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="20" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="21" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="22" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="23" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="24" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="25" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="26" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="27" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="28" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="29" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="30" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="31" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="32" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="33" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="34" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="35" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="36" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="37" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="38" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="39" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="40" s="3" customFormat="1" ht="17.399999999999999"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
@@ -1213,22 +1263,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A599C8D7-0C2F-431B-9112-234DD68856B0}">
   <dimension ref="A1:D40"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="17.125" customWidth="1"/>
-    <col min="2" max="2" width="18.625" customWidth="1"/>
-    <col min="4" max="4" width="15.625" customWidth="1"/>
+    <col min="1" max="1" width="17.109375" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="39" x14ac:dyDescent="0.75">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:4" ht="33">
+      <c r="A1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="29"/>
-    </row>
-    <row r="2" spans="1:4" s="1" customFormat="1" ht="25.5" x14ac:dyDescent="0.5">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="28"/>
+    </row>
+    <row r="2" spans="1:4" s="1" customFormat="1" ht="22.2">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1242,12 +1292,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
       <c r="A3" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="B3" s="23" t="s">
         <v>85</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>86</v>
       </c>
       <c r="C3" s="15">
         <v>0.25</v>
@@ -1256,12 +1306,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
       <c r="A4" s="13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C4" s="15">
         <v>0.25</v>
@@ -1270,12 +1320,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
       <c r="A5" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C5" s="15">
         <v>0.25</v>
@@ -1284,12 +1334,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
       <c r="A6" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C6" s="15">
         <v>1</v>
@@ -1298,12 +1348,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
       <c r="A7" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C7" s="15">
         <v>1</v>
@@ -1312,39 +1362,43 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="17" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="18" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="19" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="20" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="21" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="22" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="23" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="24" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="25" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="26" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="27" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="28" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="29" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="30" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="31" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="32" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="33" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="34" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="35" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="36" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="37" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="38" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="39" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="40" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
+    <row r="8" spans="1:4" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="9" spans="1:4" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="10" spans="1:4" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="11" spans="1:4" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="12" spans="1:4" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="13" spans="1:4" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="14" spans="1:4" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="15" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
+      <c r="A15" s="35" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="17" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="18" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="19" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="20" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="21" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="22" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="23" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="24" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="25" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="26" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="27" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="28" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="29" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="30" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="31" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="32" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="33" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="34" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="35" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="36" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="37" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="38" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="39" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="40" s="3" customFormat="1" ht="17.399999999999999"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:D1"/>
@@ -1358,22 +1412,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5506A44-B830-41AA-AFBB-8B072093ACCB}">
   <dimension ref="A1:D40"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="17.125" customWidth="1"/>
-    <col min="2" max="2" width="18.625" customWidth="1"/>
-    <col min="4" max="4" width="15.625" customWidth="1"/>
+    <col min="1" max="1" width="17.109375" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="39" x14ac:dyDescent="0.75">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:4" ht="33">
+      <c r="A1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="29"/>
-    </row>
-    <row r="2" spans="1:4" s="1" customFormat="1" ht="25.5" x14ac:dyDescent="0.5">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="28"/>
+    </row>
+    <row r="2" spans="1:4" s="1" customFormat="1" ht="22.2">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1387,7 +1441,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
       <c r="A3" s="13" t="s">
         <v>20</v>
       </c>
@@ -1401,7 +1455,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
       <c r="A4" s="17" t="s">
         <v>23</v>
       </c>
@@ -1415,7 +1469,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
       <c r="A5" s="17" t="s">
         <v>24</v>
       </c>
@@ -1429,7 +1483,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
       <c r="A6" s="17" t="s">
         <v>24</v>
       </c>
@@ -1443,7 +1497,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
       <c r="A7" s="13" t="s">
         <v>26</v>
       </c>
@@ -1457,7 +1511,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
       <c r="A8" s="13" t="s">
         <v>29</v>
       </c>
@@ -1471,7 +1525,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
       <c r="A9" s="13" t="s">
         <v>31</v>
       </c>
@@ -1485,9 +1539,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
       <c r="A10" s="13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B10" s="14" t="s">
         <v>32</v>
@@ -1499,8 +1553,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A11" s="30" t="s">
+    <row r="11" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
+      <c r="A11" s="29" t="s">
         <v>33</v>
       </c>
       <c r="B11" s="24" t="s">
@@ -1513,8 +1567,8 @@
         <v>35</v>
       </c>
     </row>
-    <row r="12" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A12" s="31"/>
+    <row r="12" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
+      <c r="A12" s="30"/>
       <c r="B12" s="3" t="s">
         <v>34</v>
       </c>
@@ -1525,8 +1579,8 @@
         <v>36</v>
       </c>
     </row>
-    <row r="13" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A13" s="31"/>
+    <row r="13" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
+      <c r="A13" s="30"/>
       <c r="B13" s="3" t="s">
         <v>38</v>
       </c>
@@ -1537,8 +1591,8 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A14" s="32"/>
+    <row r="14" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
+      <c r="A14" s="31"/>
       <c r="B14" s="20" t="s">
         <v>38</v>
       </c>
@@ -1549,7 +1603,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
       <c r="A15" s="13" t="s">
         <v>40</v>
       </c>
@@ -1563,7 +1617,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="16" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
       <c r="A16" s="13" t="s">
         <v>42</v>
       </c>
@@ -1577,76 +1631,79 @@
         <v>7</v>
       </c>
     </row>
-    <row r="17" spans="3:3" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" s="3" customFormat="1" ht="17.399999999999999">
       <c r="C17" s="8"/>
     </row>
-    <row r="18" spans="3:3" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" s="3" customFormat="1" ht="17.399999999999999">
       <c r="C18" s="8"/>
     </row>
-    <row r="19" spans="3:3" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" s="3" customFormat="1" ht="17.399999999999999">
       <c r="C19" s="8"/>
     </row>
-    <row r="20" spans="3:3" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" s="3" customFormat="1" ht="17.399999999999999">
+      <c r="A20" s="35" t="s">
+        <v>94</v>
+      </c>
       <c r="C20" s="8"/>
     </row>
-    <row r="21" spans="3:3" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" s="3" customFormat="1" ht="17.399999999999999">
       <c r="C21" s="8"/>
     </row>
-    <row r="22" spans="3:3" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" s="3" customFormat="1" ht="17.399999999999999">
       <c r="C22" s="8"/>
     </row>
-    <row r="23" spans="3:3" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" s="3" customFormat="1" ht="17.399999999999999">
       <c r="C23" s="8"/>
     </row>
-    <row r="24" spans="3:3" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" s="3" customFormat="1" ht="17.399999999999999">
       <c r="C24" s="8"/>
     </row>
-    <row r="25" spans="3:3" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" s="3" customFormat="1" ht="17.399999999999999">
       <c r="C25" s="8"/>
     </row>
-    <row r="26" spans="3:3" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" s="3" customFormat="1" ht="17.399999999999999">
       <c r="C26" s="8"/>
     </row>
-    <row r="27" spans="3:3" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" s="3" customFormat="1" ht="17.399999999999999">
       <c r="C27" s="8"/>
     </row>
-    <row r="28" spans="3:3" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" s="3" customFormat="1" ht="17.399999999999999">
       <c r="C28" s="8"/>
     </row>
-    <row r="29" spans="3:3" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" s="3" customFormat="1" ht="17.399999999999999">
       <c r="C29" s="8"/>
     </row>
-    <row r="30" spans="3:3" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" s="3" customFormat="1" ht="17.399999999999999">
       <c r="C30" s="8"/>
     </row>
-    <row r="31" spans="3:3" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" s="3" customFormat="1" ht="17.399999999999999">
       <c r="C31" s="8"/>
     </row>
-    <row r="32" spans="3:3" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" s="3" customFormat="1" ht="17.399999999999999">
       <c r="C32" s="8"/>
     </row>
-    <row r="33" spans="3:3" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:3" s="3" customFormat="1" ht="17.399999999999999">
       <c r="C33" s="8"/>
     </row>
-    <row r="34" spans="3:3" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:3" s="3" customFormat="1" ht="17.399999999999999">
       <c r="C34" s="8"/>
     </row>
-    <row r="35" spans="3:3" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="35" spans="3:3" s="3" customFormat="1" ht="17.399999999999999">
       <c r="C35" s="8"/>
     </row>
-    <row r="36" spans="3:3" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="36" spans="3:3" s="3" customFormat="1" ht="17.399999999999999">
       <c r="C36" s="8"/>
     </row>
-    <row r="37" spans="3:3" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:3" s="3" customFormat="1" ht="17.399999999999999">
       <c r="C37" s="8"/>
     </row>
-    <row r="38" spans="3:3" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="38" spans="3:3" s="3" customFormat="1" ht="17.399999999999999">
       <c r="C38" s="8"/>
     </row>
-    <row r="39" spans="3:3" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="39" spans="3:3" s="3" customFormat="1" ht="17.399999999999999">
       <c r="C39" s="8"/>
     </row>
-    <row r="40" spans="3:3" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:3" s="3" customFormat="1" ht="17.399999999999999">
       <c r="C40" s="8"/>
     </row>
   </sheetData>
@@ -1662,23 +1719,23 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8664EEE0-724F-4B35-A50F-1E6ADD09567C}">
-  <dimension ref="A1:D40"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:D43"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="17.125" customWidth="1"/>
-    <col min="2" max="2" width="18.625" customWidth="1"/>
-    <col min="4" max="4" width="15.625" customWidth="1"/>
+    <col min="1" max="1" width="17.109375" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="39" x14ac:dyDescent="0.75">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:4" ht="33">
+      <c r="A1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="29"/>
-    </row>
-    <row r="2" spans="1:4" s="1" customFormat="1" ht="25.5" x14ac:dyDescent="0.5">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="28"/>
+    </row>
+    <row r="2" spans="1:4" s="1" customFormat="1" ht="22.2">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1692,7 +1749,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
       <c r="A3" s="13" t="s">
         <v>44</v>
       </c>
@@ -1706,86 +1763,84 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A4" s="33" t="s">
+    <row r="4" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
+      <c r="A4" s="32" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="8">
+        <v>0.2</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
+      <c r="A5" s="33"/>
+      <c r="B5" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="C5" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
+      <c r="A6" s="33"/>
+      <c r="B6" s="21" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
+      <c r="A7" s="33"/>
+      <c r="B7" s="21" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
+      <c r="A8" s="33"/>
+      <c r="B8" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="C8" s="8">
+        <v>0.1</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
+      <c r="A9" s="33"/>
+      <c r="B9" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="8">
+        <v>1</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
+      <c r="A10" s="33"/>
+      <c r="B10" s="3" t="s">
         <v>47</v>
-      </c>
-      <c r="C4" s="8">
-        <v>0.5</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A5" s="34"/>
-      <c r="B5" s="21" t="s">
-        <v>45</v>
-      </c>
-      <c r="C5" s="8">
-        <v>0.25</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A6" s="34"/>
-      <c r="B6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="8">
-        <v>1</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A7" s="34"/>
-      <c r="B7" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" s="8">
-        <v>1</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A8" s="35"/>
-      <c r="B8" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="11">
-        <v>1</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A9" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="B9" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A10" s="34"/>
-      <c r="B10" s="3" t="s">
-        <v>53</v>
       </c>
       <c r="C10" s="8">
         <v>1</v>
@@ -1794,75 +1849,117 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
       <c r="A11" s="34"/>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" s="11">
+        <v>1</v>
+      </c>
+      <c r="D11" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
+      <c r="A12" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
+      <c r="A13" s="33"/>
+      <c r="B13" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="C11" s="8">
+      <c r="C13" s="8">
         <v>1</v>
       </c>
-      <c r="D11" s="9" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A12" s="35"/>
-      <c r="B12" s="20" t="s">
-        <v>60</v>
-      </c>
-      <c r="C12" s="11">
+      <c r="D13" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
+      <c r="A14" s="33"/>
+      <c r="B14" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" s="8">
         <v>1</v>
       </c>
-      <c r="D12" s="12" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A13" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="B13" s="22" t="s">
+      <c r="D14" s="9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
+      <c r="A15" s="34"/>
+      <c r="B15" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="11">
+        <v>1</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
+      <c r="A16" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="B16" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="15">
+      <c r="C16" s="15">
         <v>0.5</v>
       </c>
-      <c r="D13" s="16" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="17" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="18" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="19" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="20" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="21" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="22" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="23" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="24" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="25" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="26" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="27" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="28" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="29" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="30" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="31" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="32" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="33" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="34" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="35" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="36" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="37" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="38" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="39" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="40" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
+      <c r="D16" s="16" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="19" spans="1:1" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="20" spans="1:1" s="3" customFormat="1" ht="17.399999999999999">
+      <c r="A20" s="35" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="22" spans="1:1" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="23" spans="1:1" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="24" spans="1:1" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="25" spans="1:1" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="26" spans="1:1" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="27" spans="1:1" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="28" spans="1:1" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="29" spans="1:1" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="30" spans="1:1" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="31" spans="1:1" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="32" spans="1:1" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="33" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="34" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="35" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="36" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="37" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="38" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="39" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="40" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="41" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="42" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="43" s="3" customFormat="1" ht="17.399999999999999"/>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A4:A8"/>
-    <mergeCell ref="A9:A12"/>
+    <mergeCell ref="A4:A11"/>
+    <mergeCell ref="A12:A15"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1872,22 +1969,22 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8E1EFD30-EA2C-4DAA-86F9-DA842DEEF723}">
   <dimension ref="A1:D40"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="17.125" customWidth="1"/>
-    <col min="2" max="2" width="18.625" customWidth="1"/>
-    <col min="4" max="4" width="15.625" customWidth="1"/>
+    <col min="1" max="1" width="17.109375" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="39" x14ac:dyDescent="0.75">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:4" ht="33">
+      <c r="A1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="29"/>
-    </row>
-    <row r="2" spans="1:4" s="1" customFormat="1" ht="25.5" x14ac:dyDescent="0.5">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="28"/>
+    </row>
+    <row r="2" spans="1:4" s="1" customFormat="1" ht="22.2">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1901,12 +1998,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
       <c r="A3" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="14" t="s">
         <v>54</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>55</v>
       </c>
       <c r="C3" s="15">
         <v>0.15</v>
@@ -1915,9 +2012,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
       <c r="A4" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B4" s="14" t="s">
         <v>9</v>
@@ -1929,12 +2026,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A5" s="30" t="s">
+    <row r="5" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
+      <c r="A5" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="B5" s="20" t="s">
         <v>56</v>
-      </c>
-      <c r="B5" s="20" t="s">
-        <v>57</v>
       </c>
       <c r="C5" s="11">
         <v>1</v>
@@ -1943,10 +2040,10 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A6" s="32"/>
+    <row r="6" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
+      <c r="A6" s="31"/>
       <c r="B6" s="20" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C6" s="11">
         <v>1</v>
@@ -1955,53 +2052,53 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
       <c r="A7" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="B7" s="20" t="s">
         <v>61</v>
-      </c>
-      <c r="B7" s="20" t="s">
-        <v>62</v>
       </c>
       <c r="C7" s="11">
         <v>1</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="9" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="10" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="11" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="14" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="15" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="16" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="17" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="18" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="19" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="20" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="21" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="22" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="23" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="24" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="25" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="26" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="27" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="28" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="29" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="30" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="31" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="32" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="33" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="34" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="35" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="36" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="37" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="38" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="39" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="40" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
+        <v>83</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="9" spans="1:4" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="10" spans="1:4" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="11" spans="1:4" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="12" spans="1:4" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="13" spans="1:4" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="14" spans="1:4" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="15" spans="1:4" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="16" spans="1:4" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="17" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="18" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="19" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="20" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="21" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="22" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="23" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="24" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="25" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="26" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="27" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="28" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="29" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="30" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="31" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="32" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="33" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="34" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="35" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="36" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="37" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="38" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="39" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="40" s="3" customFormat="1" ht="17.399999999999999"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
@@ -2015,22 +2112,22 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66E2DE70-42AF-4022-9753-A6F760C964BA}">
   <dimension ref="A1:D40"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="17.125" customWidth="1"/>
-    <col min="2" max="2" width="18.625" customWidth="1"/>
-    <col min="4" max="4" width="15.625" customWidth="1"/>
+    <col min="1" max="1" width="17.109375" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="39" x14ac:dyDescent="0.75">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:4" ht="33">
+      <c r="A1" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="29"/>
-    </row>
-    <row r="2" spans="1:4" s="1" customFormat="1" ht="25.5" x14ac:dyDescent="0.5">
+      <c r="B1" s="27"/>
+      <c r="C1" s="27"/>
+      <c r="D1" s="28"/>
+    </row>
+    <row r="2" spans="1:4" s="1" customFormat="1" ht="22.2">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -2044,12 +2141,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
       <c r="A3" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C3" s="15">
         <v>0.15</v>
@@ -2058,12 +2155,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
       <c r="A4" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C4" s="15">
         <v>0.15</v>
@@ -2072,9 +2169,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
       <c r="A5" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B5" s="22" t="s">
         <v>30</v>
@@ -2086,12 +2183,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
       <c r="A6" s="13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C6" s="15">
         <v>0.25</v>
@@ -2100,12 +2197,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
       <c r="A7" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>82</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>83</v>
       </c>
       <c r="C7" s="15">
         <v>0.25</v>
@@ -2114,12 +2211,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
       <c r="A8" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B8" s="22" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C8" s="15">
         <v>0.15</v>
@@ -2128,12 +2225,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
       <c r="A9" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" s="14" t="s">
         <v>80</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>81</v>
       </c>
       <c r="C9" s="15">
         <v>0.25</v>
@@ -2142,12 +2239,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
       <c r="A10" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B10" s="14" t="s">
         <v>78</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>79</v>
       </c>
       <c r="C10" s="15">
         <v>0.25</v>
@@ -2156,12 +2253,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
       <c r="A11" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="14" t="s">
         <v>74</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>75</v>
       </c>
       <c r="C11" s="15">
         <v>0.25</v>
@@ -2170,12 +2267,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A12" s="30" t="s">
+    <row r="12" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
+      <c r="A12" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>76</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>77</v>
       </c>
       <c r="C12" s="5">
         <v>0.25</v>
@@ -2184,9 +2281,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="13" spans="1:4" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A13" s="32"/>
-      <c r="B13" s="27" t="s">
+    <row r="13" spans="1:4" s="3" customFormat="1" ht="17.399999999999999">
+      <c r="A13" s="31"/>
+      <c r="B13" s="26" t="s">
         <v>6</v>
       </c>
       <c r="C13" s="11">
@@ -2196,27 +2293,31 @@
         <v>7</v>
       </c>
     </row>
-    <row r="20" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="21" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="22" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="23" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="24" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="25" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="26" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="27" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="28" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="29" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="30" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="31" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="32" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="33" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="34" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="35" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="36" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="37" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="38" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="39" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
-    <row r="40" s="3" customFormat="1" ht="17.25" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:1" s="3" customFormat="1" ht="17.399999999999999">
+      <c r="A20" s="35" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="22" spans="1:1" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="23" spans="1:1" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="24" spans="1:1" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="25" spans="1:1" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="26" spans="1:1" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="27" spans="1:1" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="28" spans="1:1" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="29" spans="1:1" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="30" spans="1:1" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="31" spans="1:1" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="32" spans="1:1" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="33" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="34" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="35" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="36" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="37" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="38" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="39" s="3" customFormat="1" ht="17.399999999999999"/>
+    <row r="40" s="3" customFormat="1" ht="17.399999999999999"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:D1"/>
